--- a/Data/India_GS.xlsx
+++ b/Data/India_GS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,849 +472,849 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which state has the highest literacy rate in India?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which is the longest river in India?</t>
+          <t>Which state has the highest literacy rate in India?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the capital of India?</t>
+          <t>Which country shares the longest border with India?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which city is known as the Silicon Valley of India?</t>
+          <t>Which Indian city is known for the Golden Temple?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which Indian state has the largest area?</t>
+          <t>Which river is considered the holiest river in India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>India shares its border with how many countries?</t>
+          <t>Which Indian dance form originated in Kerala?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Kathak</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Odissi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Bharatanatyam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Indian city is called the Pink City?</t>
+          <t>Which city is called the Yoga Capital of the World?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Haridwar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the national bird of India?</t>
+          <t>Which dam is the largest in India?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Sardar Sarovar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Hirakud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which river is known as the 'Dakshina Ganga'?</t>
+          <t>Which Indian state is the largest producer of spices?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kaveri</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which state is the largest producer of wheat in India?</t>
+          <t>Which Indian scientist invented the ‘zero’?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Bhaskara I</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Ramanujan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which Indian state is famous for backwaters?</t>
+          <t>Which Indian city is known as the Manchester of India?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Indian city is called the City of Joy?</t>
+          <t>What is India’s GDP rank globally in 2024?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which dam is the largest in India?</t>
+          <t>Which is the first satellite launched by India?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sardar Sarovar</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Bhaskara</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hirakud</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What is the national fruit of India?</t>
+          <t>Which Indian state is the largest tea producer?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in India?</t>
+          <t>What is the national fruit of India?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which state is known as the Spice Garden of India?</t>
+          <t>Which is the oldest mountain range in India?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Himalayas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Vindhyas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Aravallis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Satpuras</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Aravallis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is the most populous state in India?</t>
+          <t>Which is the highest mountain peak in India?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Indian festival is known as the festival of lights?</t>
+          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Baisakhi</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dussehra</t>
+          <t>Gateway of India</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which Indian festival celebrates the brother-sister bond?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Raksha Bandhan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Janmashtami</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Raksha Bandhan</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
+          <t>Which Indian monument is known as the symbol of eternal love?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Taj Mahal</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Charminar</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gateway of India</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which state is famous for the Sun Temple at Konark?</t>
+          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Indian river is considered the most sacred?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>CV Raman</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
+          <t>Which Indian personality won the first Oscar award?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Satyajit Ray</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>A. R. Rahman</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Resul Pookutty</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which state has two capitals (summer and winter)?</t>
+          <t>Which Indian state is known for maximum sugar production?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1324,1319 +1324,1319 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which city is known as the Cleanest City in India (2023)?</t>
+          <t>When was the Indian Constitution adopted?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>In which year did India gain independence?</t>
+          <t>Which city is known as the Cleanest City in India (2023)?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>How many IITs are there in India as of 2024?</t>
+          <t>In which year did India gain independence?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is India's global rank in military strength (2024)?</t>
+          <t>How many states are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is India’s GDP rank globally in 2024?</t>
+          <t>Who was the first woman Prime Minister of India?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which sector contributes the most to India's GDP?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Indian state has the longest coastline?</t>
+          <t>What is the oldest university in India?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>University of Delhi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Banaras Hindu University</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Aligarh Muslim University</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>When was the Indian Constitution adopted?</t>
+          <t>Which Indian state has its own constitution?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>How many official languages are recognized in the Indian Constitution?</t>
+          <t>What is India's global rank in military strength (2024)?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who is known as the Missile Man of India?</t>
+          <t>How many IITs are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What is India's rank in global smartphone usage (2024)?</t>
+          <t>Which Indian state is famous for backwaters?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which sector contributes the most to India's GDP?</t>
+          <t>Which state is famous for the Sun Temple at Konark?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which is the first satellite launched by India?</t>
+          <t>Who is known as the Missile Man of India?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bhaskara</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>When was GST (Goods and Services Tax) implemented in India?</t>
+          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Ghaghara</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Indian city hosted the first Asian Games?</t>
+          <t>Which state has two capitals (summer and winter)?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How many states are there in India as of 2024?</t>
+          <t>What is India's rank in global smartphone usage (2024)?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which country shares the longest border with India?</t>
+          <t>India shares its border with how many countries?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest tea producer?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What is the full form of ISRO?</t>
+          <t>Which state in India is famous for Chhau dance?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>International Space Research Operation</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Indian Satellite Research Office</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Indian Science Research Organization</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>What is the capital of India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CV Raman</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Indian state is known for maximum sugar production?</t>
+          <t>Which Indian state is the largest producer of silk?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Karnataka</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Maharashtra</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Where is the headquarters of the Reserve Bank of India?</t>
+          <t>What is the name of the Indian Parliament building?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Rashtrapati Bhavan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Vidhan Sabha</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>Which state is the largest producer of wheat in India?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the Manchester of India?</t>
+          <t>Which is the most populous state in India?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which is the oldest mountain range in India?</t>
+          <t>Which is India’s first underwater metro project city?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Himalayas</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Vindhyas</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aravallis</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Satpuras</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aravallis</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which state is the leading producer of cotton in India?</t>
+          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Indian monument is known as the symbol of eternal love?</t>
+          <t>When was GST (Goods and Services Tax) implemented in India?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
+          <t>What is the national bird of India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
+          <t>Which Indian state has the longest coastline?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which city is called the Yoga Capital of the World?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Haridwar</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which Indian state celebrates Hornbill Festival?</t>
+          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
+          <t>Which Indian city is called the City of Joy?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is the name of the Indian Parliament building?</t>
+          <t>How many official languages are recognized in the Indian Constitution?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Rashtrapati Bhavan</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister of India?</t>
+          <t>Which Indian river is considered the most sacred?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the City of Lakes?</t>
+          <t>Where is the headquarters of the Reserve Bank of India?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nainital</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Indian personality won the first Oscar award?</t>
+          <t>Which city is known as the Silicon Valley of India?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Satyajit Ray</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>A. R. Rahman</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Resul Pookutty</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of spices?</t>
+          <t>Which state is known as the Spice Garden of India?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2668,47 +2668,47 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which river is considered the holiest river in India?</t>
+          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
+          <t>Which Indian city hosted the first Asian Games?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2718,17 +2718,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2740,432 +2740,432 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which Indian festival celebrates the brother-sister bond?</t>
+          <t>What is the full form of ISRO?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Raksha Bandhan</t>
+          <t>International Space Research Operation</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>Indian Satellite Research Office</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Janmashtami</t>
+          <t>Indian Science Research Organization</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Raksha Bandhan</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What is the oldest university in India?</t>
+          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>University of Delhi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Banaras Hindu University</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aligarh Muslim University</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which Indian dance form originated in Kerala?</t>
+          <t>Which Indian state celebrates Hornbill Festival?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kathak</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Odissi</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bharatanatyam</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of silk?</t>
+          <t>Which Indian state has the largest area?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which state in India is famous for Chhau dance?</t>
+          <t>Which is the longest river in India?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Indian city is known for the Golden Temple?</t>
+          <t>Which Indian festival is known as the festival of lights?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Baisakhi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Dussehra</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Indian state has its own constitution?</t>
+          <t>What is the highest civilian award in India?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Padma Bhushan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Padma Shri</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Param Vir Chakra</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
+          <t>Which Indian city is called the Pink City?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ghaghara</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What is the highest civilian award in India?</t>
+          <t>Which river is known as the 'Dakshina Ganga'?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Padma Bhushan</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Padma Shri</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Param Vir Chakra</t>
+          <t>Kaveri</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Indian scientist invented the ‘zero’?</t>
+          <t>Which Indian city is known as the City of Lakes?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bhaskara I</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ramanujan</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which is India’s first underwater metro project city?</t>
+          <t>Which Indian island is known for active volcanoes?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Minicoy</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Little Andaman</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Indian island is known for active volcanoes?</t>
+          <t>Which state is the leading producer of cotton in India?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Minicoy</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Little Andaman</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/India_GS.xlsx
+++ b/Data/India_GS.xlsx
@@ -472,1523 +472,1523 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is India's rank in global smartphone usage (2024)?</t>
+          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in India?</t>
+          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the name of the Indian Parliament building?</t>
+          <t>Which Indian state is the largest producer of silk?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rashtrapati Bhavan</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>Which is the oldest mountain range in India?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Himalayas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Vindhyas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Aravallis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Satpuras</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Aravallis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which state has two capitals (summer and winter)?</t>
+          <t>Which is the longest river in India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which is the longest river in India?</t>
+          <t>Which state has two capitals (summer and winter)?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which is the oldest mountain range in India?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Himalayas</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vindhyas</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aravallis</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Satpuras</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aravallis</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of silk?</t>
+          <t>What is the name of the Indian Parliament building?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Rashtrapati Bhavan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Vidhan Sabha</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
+          <t>Which is the highest mountain peak in India?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
+          <t>What is India's rank in global smartphone usage (2024)?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which Indian monument is known as the symbol of eternal love?</t>
+          <t>Which Indian state has its own constitution?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When was the Indian Constitution adopted?</t>
+          <t>Which river is known as the 'Dakshina Ganga'?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Kaveri</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Indian state has the largest area?</t>
+          <t>Which city is called the Yoga Capital of the World?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Haridwar</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How many official languages are recognized in the Indian Constitution?</t>
+          <t>Which dam is the largest in India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Sardar Sarovar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Hirakud</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which city is known as the Cleanest City in India (2023)?</t>
+          <t>Which Indian state is known for maximum sugar production?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Indian state is known for maximum sugar production?</t>
+          <t>Which city is known as the Cleanest City in India (2023)?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which dam is the largest in India?</t>
+          <t>How many official languages are recognized in the Indian Constitution?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sardar Sarovar</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hirakud</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which city is called the Yoga Capital of the World?</t>
+          <t>Which Indian state has the largest area?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Haridwar</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which river is known as the 'Dakshina Ganga'?</t>
+          <t>When was the Indian Constitution adopted?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaveri</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which Indian state has its own constitution?</t>
+          <t>Which Indian monument is known as the symbol of eternal love?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What is India's global rank in military strength (2024)?</t>
+          <t>Which Indian city is called the City of Joy?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which state is known as the Spice Garden of India?</t>
+          <t>What is the full form of ISRO?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>International Space Research Operation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Indian Satellite Research Office</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Indian Science Research Organization</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which Indian personality won the first Oscar award?</t>
+          <t>Which Indian city is known for the Golden Temple?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Satyajit Ray</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A. R. Rahman</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Resul Pookutty</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
+          <t>Which Indian scientist invented the ‘zero’?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Bhaskara I</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>Ramanujan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gateway of India</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>In which year did India gain independence?</t>
+          <t>Which Indian city is known as the Manchester of India?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the Manchester of India?</t>
+          <t>In which year did India gain independence?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Indian scientist invented the ‘zero’?</t>
+          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bhaskara I</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ramanujan</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Gateway of India</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Indian city is known for the Golden Temple?</t>
+          <t>Which Indian personality won the first Oscar award?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Satyajit Ray</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>A. R. Rahman</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Resul Pookutty</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the full form of ISRO?</t>
+          <t>Which state is known as the Spice Garden of India?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>International Space Research Operation</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Indian Satellite Research Office</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Indian Science Research Organization</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Indian city is called the City of Joy?</t>
+          <t>What is India's global rank in military strength (2024)?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Indian state celebrates Hornbill Festival?</t>
+          <t>Which Indian state is famous for backwaters?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>India shares its border with how many countries?</t>
+          <t>Which Indian dance form originated in Kerala?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Kathak</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Odissi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Bharatanatyam</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>How many states are there in India as of 2024?</t>
+          <t>What is the national bird of India?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
+          <t>What is the capital of India?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which sector contributes the most to India's GDP?</t>
+          <t>Which Indian state has the longest coastline?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Indian state has the longest coastline?</t>
+          <t>Which sector contributes the most to India's GDP?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What is the capital of India?</t>
+          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>New Delhi</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What is the national bird of India?</t>
+          <t>How many states are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Indian dance form originated in Kerala?</t>
+          <t>India shares its border with how many countries?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kathak</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Odissi</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bharatanatyam</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Indian state is famous for backwaters?</t>
+          <t>Which Indian state celebrates Hornbill Festival?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which country shares the longest border with India?</t>
+          <t>What is the highest civilian award in India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Padma Bhushan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Padma Shri</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Param Vir Chakra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who is known as the Missile Man of India?</t>
+          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Ghaghara</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which state is the largest producer of wheat in India?</t>
+          <t>Which state is the leading producer of cotton in India?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1998,177 +1998,177 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What is the national fruit of India?</t>
+          <t>Which Indian island is known for active volcanoes?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Minicoy</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Little Andaman</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
+          <t>Which Indian state is the largest producer of spices?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of spices?</t>
+          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Indian island is known for active volcanoes?</t>
+          <t>What is the national fruit of India?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Minicoy</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Little Andaman</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which state is the leading producer of cotton in India?</t>
+          <t>Which state is the largest producer of wheat in India?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2178,105 +2178,105 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
+          <t>Who is known as the Missile Man of India?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ghaghara</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the highest civilian award in India?</t>
+          <t>Which country shares the longest border with India?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Padma Bhushan</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Padma Shri</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Param Vir Chakra</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which state is famous for the Sun Temple at Konark?</t>
+          <t>Which state in India is famous for Chhau dance?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2308,299 +2308,299 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which is the first satellite launched by India?</t>
+          <t>When was GST (Goods and Services Tax) implemented in India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bhaskara</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Indian river is considered the most sacred?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which city is known as the Silicon Valley of India?</t>
+          <t>Which is the most populous state in India?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is the oldest university in India?</t>
+          <t>Who was the first woman Prime Minister of India?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>University of Delhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Banaras Hindu University</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aligarh Muslim University</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister of India?</t>
+          <t>What is the oldest university in India?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>University of Delhi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Banaras Hindu University</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Aligarh Muslim University</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which is the most populous state in India?</t>
+          <t>Which city is known as the Silicon Valley of India?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which Indian river is considered the most sacred?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>When was GST (Goods and Services Tax) implemented in India?</t>
+          <t>Which is the first satellite launched by India?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>Bhaskara</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which state in India is famous for Chhau dance?</t>
+          <t>Which state is famous for the Sun Temple at Konark?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2632,432 +2632,432 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which state has the highest literacy rate in India?</t>
+          <t>How many IITs are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the City of Lakes?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Nainital</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Indian city hosted the first Asian Games?</t>
+          <t>Which Indian festival is known as the festival of lights?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Baisakhi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Dussehra</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Where is the headquarters of the Reserve Bank of India?</t>
+          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which river is considered the holiest river in India?</t>
+          <t>Which Indian city is called the Pink City?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which Indian city is called the Pink City?</t>
+          <t>Which river is considered the holiest river in India?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
+          <t>Where is the headquarters of the Reserve Bank of India?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which Indian festival is known as the festival of lights?</t>
+          <t>Which Indian city hosted the first Asian Games?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Baisakhi</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dussehra</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which Indian city is known as the City of Lakes?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>How many IITs are there in India as of 2024?</t>
+          <t>Which state has the highest literacy rate in India?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What is India’s GDP rank globally in 2024?</t>
+          <t>Which is India’s first underwater metro project city?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest tea producer?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>CV Raman</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3100,72 +3100,72 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>Which Indian state is the largest tea producer?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CV Raman</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which is India’s first underwater metro project city?</t>
+          <t>What is India’s GDP rank globally in 2024?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/India_GS.xlsx
+++ b/Data/India_GS.xlsx
@@ -472,108 +472,108 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
+          <t>When was GST (Goods and Services Tax) implemented in India?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
+          <t>Which city is called the Yoga Capital of the World?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Haridwar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of silk?</t>
+          <t>Which Indian river is considered the most sacred?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -616,1548 +616,1548 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which is the longest river in India?</t>
+          <t>What is the national bird of India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which state has two capitals (summer and winter)?</t>
+          <t>Which Indian state celebrates Hornbill Festival?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>Which Indian state is known for maximum sugar production?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the name of the Indian Parliament building?</t>
+          <t>Which Indian city is known for the Golden Temple?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rashtrapati Bhavan</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in India?</t>
+          <t>Which city is known as the Silicon Valley of India?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is India's rank in global smartphone usage (2024)?</t>
+          <t>Which Indian personality won the first Oscar award?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>Satyajit Ray</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>A. R. Rahman</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Resul Pookutty</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which Indian state has its own constitution?</t>
+          <t>Which state in India is famous for Chhau dance?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Manipur</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Sikkim</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jammu &amp; Kashmir</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Goa</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Nagaland</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which river is known as the 'Dakshina Ganga'?</t>
+          <t>Which is the longest river in India?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Ganga</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Godavari</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Kaveri</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which city is called the Yoga Capital of the World?</t>
+          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Haridwar</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Ghaghara</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which dam is the largest in India?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sardar Sarovar</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hirakud</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Indian state is known for maximum sugar production?</t>
+          <t>In which year did India gain independence?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which city is known as the Cleanest City in India (2023)?</t>
+          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>How many official languages are recognized in the Indian Constitution?</t>
+          <t>Which is the first satellite launched by India?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Bhaskara</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Indian state has the largest area?</t>
+          <t>Which dam is the largest in India?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Sardar Sarovar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Hirakud</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When was the Indian Constitution adopted?</t>
+          <t>Who is known as the Missile Man of India?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which Indian monument is known as the symbol of eternal love?</t>
+          <t>Which river is known as the 'Dakshina Ganga'?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>Kaveri</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Indian city is called the City of Joy?</t>
+          <t>How many states are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is the full form of ISRO?</t>
+          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>International Space Research Operation</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Indian Satellite Research Office</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Indian Science Research Organization</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which Indian city is known for the Golden Temple?</t>
+          <t>What is the name of the Indian Parliament building?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Rashtrapati Bhavan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Vidhan Sabha</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Indian scientist invented the ‘zero’?</t>
+          <t>Which Indian state is the largest tea producer?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bhaskara I</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ramanujan</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the Manchester of India?</t>
+          <t>When was the Indian Constitution adopted?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>In which year did India gain independence?</t>
+          <t>Which Indian city hosted the first Asian Games?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
+          <t>What is the highest civilian award in India?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Padma Bhushan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>Padma Shri</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gateway of India</t>
+          <t>Param Vir Chakra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Indian personality won the first Oscar award?</t>
+          <t>Which Indian state is the largest producer of silk?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Satyajit Ray</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A. R. Rahman</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Resul Pookutty</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which state is known as the Spice Garden of India?</t>
+          <t>What is the national fruit of India?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What is India's global rank in military strength (2024)?</t>
+          <t>Which Indian city is called the City of Joy?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Indian state is famous for backwaters?</t>
+          <t>Which river is considered the holiest river in India?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Indian dance form originated in Kerala?</t>
+          <t>Which Indian festival is known as the festival of lights?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kathak</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Odissi</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bharatanatyam</t>
+          <t>Baisakhi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>Dussehra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the national bird of India?</t>
+          <t>Which Indian island is known for active volcanoes?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Minicoy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Little Andaman</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What is the capital of India?</t>
+          <t>How many official languages are recognized in the Indian Constitution?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Indian state has the longest coastline?</t>
+          <t>Which city is known as the Cleanest City in India (2023)?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which sector contributes the most to India's GDP?</t>
+          <t>India shares its border with how many countries?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
+          <t>Which Indian monument is known as the symbol of eternal love?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>How many states are there in India as of 2024?</t>
+          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>India shares its border with how many countries?</t>
+          <t>What is India’s GDP rank globally in 2024?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Indian state celebrates Hornbill Festival?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>CV Raman</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the highest civilian award in India?</t>
+          <t>Which Indian state is the largest producer of spices?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Padma Bhushan</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Padma Shri</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Param Vir Chakra</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
+          <t>Which Indian city is known as the Manchester of India?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ghaghara</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which state is the leading producer of cotton in India?</t>
+          <t>Who was the first woman Prime Minister of India?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Indian island is known for active volcanoes?</t>
+          <t>What is the oldest university in India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>University of Delhi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Minicoy</t>
+          <t>Banaras Hindu University</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Little Andaman</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Aligarh Muslim University</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of spices?</t>
+          <t>Where is the headquarters of the Reserve Bank of India?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
+          <t>Which is India’s first underwater metro project city?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is the national fruit of India?</t>
+          <t>Which Indian state has the longest coastline?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2200,391 +2200,391 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who is known as the Missile Man of India?</t>
+          <t>Which country shares the longest border with India?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which country shares the longest border with India?</t>
+          <t>What is the full form of ISRO?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>International Space Research Operation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Indian Satellite Research Office</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Indian Science Research Organization</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which state in India is famous for Chhau dance?</t>
+          <t>Which is the highest mountain peak in India?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>When was GST (Goods and Services Tax) implemented in India?</t>
+          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Gateway of India</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which is the most populous state in India?</t>
+          <t>Which Indian city is known as the City of Lakes?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister of India?</t>
+          <t>What is India's rank in global smartphone usage (2024)?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is the oldest university in India?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>University of Delhi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Banaras Hindu University</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aligarh Muslim University</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which city is known as the Silicon Valley of India?</t>
+          <t>Which Indian state is famous for backwaters?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Indian river is considered the most sacred?</t>
+          <t>Which state is famous for the Sun Temple at Konark?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which is the first satellite launched by India?</t>
+          <t>Which Indian scientist invented the ‘zero’?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Bhaskara I</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bhaskara</t>
+          <t>Ramanujan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2596,576 +2596,576 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which state is famous for the Sun Temple at Konark?</t>
+          <t>Which is the most populous state in India?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>How many IITs are there in India as of 2024?</t>
+          <t>Which sector contributes the most to India's GDP?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which Indian dance form originated in Kerala?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Kathak</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>Odissi</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Bharatanatyam</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Indian festival is known as the festival of lights?</t>
+          <t>How many IITs are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Baisakhi</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dussehra</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
+          <t>Which state is the leading producer of cotton in India?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which Indian city is called the Pink City?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which river is considered the holiest river in India?</t>
+          <t>Which state has the highest literacy rate in India?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Where is the headquarters of the Reserve Bank of India?</t>
+          <t>Which Indian festival celebrates the brother-sister bond?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Raksha Bandhan</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Janmashtami</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Raksha Bandhan</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which Indian city hosted the first Asian Games?</t>
+          <t>Which state is known as the Spice Garden of India?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the City of Lakes?</t>
+          <t>What is India's global rank in military strength (2024)?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nainital</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which state has the highest literacy rate in India?</t>
+          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which is India’s first underwater metro project city?</t>
+          <t>Which state has two capitals (summer and winter)?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>Which Indian state has its own constitution?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CV Raman</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Indian festival celebrates the brother-sister bond?</t>
+          <t>Which Indian city is called the Pink City?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Raksha Bandhan</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Janmashtami</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Raksha Bandhan</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest tea producer?</t>
+          <t>What is the capital of India?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What is India’s GDP rank globally in 2024?</t>
+          <t>Which Indian state has the largest area?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/India_GS.xlsx
+++ b/Data/India_GS.xlsx
@@ -472,864 +472,864 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When was GST (Goods and Services Tax) implemented in India?</t>
+          <t>Which Indian island is known for active volcanoes?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>Minicoy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>Little Andaman</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>Barren Island</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which city is called the Yoga Capital of the World?</t>
+          <t>Which Indian city is known as the Manchester of India?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Haridwar</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rishikesh</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Indian river is considered the most sacred?</t>
+          <t>Which dam is the largest in India?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Sardar Sarovar</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Bhakra Nangal</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Hirakud</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Tehri Dam</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which is the oldest mountain range in India?</t>
+          <t>Which Indian river is considered the most sacred?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Himalayas</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vindhyas</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aravallis</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Satpuras</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aravallis</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What is the national bird of India?</t>
+          <t>Which state in India is famous for Chhau dance?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which Indian state celebrates Hornbill Festival?</t>
+          <t>Which city is known as the Silicon Valley of India?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Indian state is known for maximum sugar production?</t>
+          <t>Which state is the largest producer of wheat in India?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Indian city is known for the Golden Temple?</t>
+          <t>How many official languages are recognized in the Indian Constitution?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which city is known as the Silicon Valley of India?</t>
+          <t>Which is the longest river in India?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Brahmaputra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Indian personality won the first Oscar award?</t>
+          <t>Which Indian state is the largest producer of silk?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Satyajit Ray</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A. R. Rahman</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Resul Pookutty</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bhanu Athaiya</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which state in India is famous for Chhau dance?</t>
+          <t>Which Indian airport is the busiest by passenger traffic?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which is the longest river in India?</t>
+          <t>Which river is known as the 'Dakshina Ganga'?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brahmaputra</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Kaveri</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Godavari</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Ganga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
+          <t>What is the full form of ISRO?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>International Space Research Operation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Indian Satellite Research Office</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghaghara</t>
+          <t>Indian Science Research Organization</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kosi</t>
+          <t>Indian Space Research Organization</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister of India?</t>
+          <t>Which country shares the longest border with India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sardar Patel</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>In which year did India gain independence?</t>
+          <t>Which Indian state has the largest area?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
+          <t>Which is the most populous state in India?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is the first satellite launched by India?</t>
+          <t>Which is the smallest state in India by area?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INSAT-1A</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bhaskara</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which dam is the largest in India?</t>
+          <t>Which Indian scientist invented the ‘zero’?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sardar Sarovar</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bhakra Nangal</t>
+          <t>Bhaskara I</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Ramanujan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hirakud</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tehri Dam</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who is known as the Missile Man of India?</t>
+          <t>In which year did India gain independence?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rakesh Sharma</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which river is known as the 'Dakshina Ganga'?</t>
+          <t>Which Indian state celebrates Hornbill Festival?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaveri</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>How many states are there in India as of 2024?</t>
+          <t>Which state has the highest literacy rate in India?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
+          <t>Which river is considered the holiest river in India?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is the name of the Indian Parliament building?</t>
+          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rashtrapati Bhavan</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vidhan Sabha</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sansad Bhavan</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest tea producer?</t>
+          <t>What is India's global rank in military strength (2024)?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1372,93 +1372,93 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Indian city hosted the first Asian Games?</t>
+          <t>Which is the highest mountain peak in India?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Nanda Devi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Kanchenjunga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the highest civilian award in India?</t>
+          <t>How many IITs are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Padma Bhushan</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Padma Shri</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Param Vir Chakra</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bharat Ratna</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of silk?</t>
+          <t>Which state is famous for the Sun Temple at Konark?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1468,455 +1468,455 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the national fruit of India?</t>
+          <t>Which Indian city is known as the City of Lakes?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Nainital</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Indian city is called the City of Joy?</t>
+          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Surat</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ahmedabad</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which river is considered the holiest river in India?</t>
+          <t>Which Indian city is called the City of Joy?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Indian festival is known as the festival of lights?</t>
+          <t>What is the capital of India?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baisakhi</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dussehra</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which Indian island is known for active volcanoes?</t>
+          <t>Which Indian state has the highest number of UNESCO World Heritage Sites?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Minicoy</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Little Andaman</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Barren Island</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How many official languages are recognized in the Indian Constitution?</t>
+          <t>Which is the first satellite launched by India?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>INSAT-1A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Bhaskara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Aryabhata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which city is known as the Cleanest City in India (2023)?</t>
+          <t>Which Indian city is called the Pink City?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>India shares its border with how many countries?</t>
+          <t>Which Indian river is known as the ‘Sorrow of Bihar’?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Ghaghara</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Kosi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Indian monument is known as the symbol of eternal love?</t>
+          <t>What is the highest civilian award in India?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>Padma Bhushan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Red Fort</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Padma Shri</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>Param Vir Chakra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Taj Mahal</t>
+          <t>Bharat Ratna</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Indian city is famous for its diamond cutting and polishing industry?</t>
+          <t>Which state has two capitals (summer and winter)?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What is India’s GDP rank globally in 2024?</t>
+          <t>What is the national bird of India?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who was the first Indian to win a Nobel Prize?</t>
+          <t>Which Indian state is the largest tea producer?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CV Raman</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mother Teresa</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kailash Satyarthi</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rabindranath Tagore</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Indian state is the largest producer of spices?</t>
+          <t>Which state is known as the Spice Garden of India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1948,659 +1948,659 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the Manchester of India?</t>
+          <t>When was GST (Goods and Services Tax) implemented in India?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Who was the first woman Prime Minister of India?</t>
+          <t>Which city is known as the Cleanest City in India (2023)?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What is the oldest university in India?</t>
+          <t>Who is known as the Missile Man of India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>University of Delhi</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Banaras Hindu University</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aligarh Muslim University</t>
+          <t>Rakesh Sharma</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nalanda University</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Where is the headquarters of the Reserve Bank of India?</t>
+          <t>Which Indian dance form originated in Kerala?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kathak</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Odissi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bharatanatyam</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kathakali</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which is India’s first underwater metro project city?</t>
+          <t>What is the oldest university in India?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>University of Delhi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Banaras Hindu University</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Aligarh Muslim University</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Nalanda University</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Indian state has the longest coastline?</t>
+          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Homi Bhabha</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Vikram Sarabhai</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>M. S. Swaminathan</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which state is the largest producer of wheat in India?</t>
+          <t>Who was the first Indian to win a Nobel Prize?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>CV Raman</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Mother Teresa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Kailash Satyarthi</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Rabindranath Tagore</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which country shares the longest border with India?</t>
+          <t>What is India's rank in global smartphone usage (2024)?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the full form of ISRO?</t>
+          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>International Space Research Operation</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Indian Satellite Research Office</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Indian Science Research Organization</t>
+          <t>Gateway of India</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Indian Space Research Organization</t>
+          <t>Qutub Minar</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which is the highest mountain peak in India?</t>
+          <t>Which Indian monument is known as the symbol of eternal love?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>India Gate</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Red Fort</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanda Devi</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mount Everest</t>
+          <t>Charminar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kanchenjunga</t>
+          <t>Taj Mahal</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Indian scientist is known as the father of India’s Green Revolution?</t>
+          <t>What is the national fruit of India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Homi Bhabha</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vikram Sarabhai</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Indian monument is a UNESCO World Heritage Site?</t>
+          <t>Which Indian personality won the first Oscar award?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Satyajit Ray</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>India Gate</t>
+          <t>A. R. Rahman</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Charminar</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gateway of India</t>
+          <t>Resul Pookutty</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Qutub Minar</t>
+          <t>Bhanu Athaiya</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Indian city is known as the City of Lakes?</t>
+          <t>Which Indian festival is known as the festival of lights?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nainital</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Baisakhi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Srinagar</t>
+          <t>Dussehra</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is India's rank in global smartphone usage (2024)?</t>
+          <t>Which Indian city hosted the first Asian Games?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Indian airport is the busiest by passenger traffic?</t>
+          <t>How many states are there in India as of 2024?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Indian state is famous for backwaters?</t>
+          <t>Which Indian state has its own constitution?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Sikkim</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Jammu &amp; Kashmir</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Goa</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Tamil Nadu</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Kerala</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jammu &amp; Kashmir</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which state is famous for the Sun Temple at Konark?</t>
+          <t>Which state is the leading producer of cotton in India?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Indian scientist invented the ‘zero’?</t>
+          <t>Which is India’s first underwater metro project city?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bhaskara I</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ramanujan</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Aryabhata</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which is the most populous state in India?</t>
+          <t>Which Indian state is known for maximum sugar production?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2610,285 +2610,285 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which sector contributes the most to India's GDP?</t>
+          <t>Which is the oldest mountain range in India?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Himalayas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Vindhyas</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Aravallis</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Satpuras</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Aravallis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which Indian dance form originated in Kerala?</t>
+          <t>Which Indian state is famous for backwaters?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kathak</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Odissi</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bharatanatyam</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kathakali</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>How many IITs are there in India as of 2024?</t>
+          <t>Where is the Indian Space Research Organisation (ISRO) headquartered?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which state is the leading producer of cotton in India?</t>
+          <t>Who was the first woman Prime Minister of India?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which is the smallest state in India by area?</t>
+          <t>Which Indian festival celebrates the brother-sister bond?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Diwali</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Raksha Bandhan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Holi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Janmashtami</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Raksha Bandhan</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which state has the highest literacy rate in India?</t>
+          <t>Which Indian city is known for the Golden Temple?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Indian festival celebrates the brother-sister bond?</t>
+          <t>Who was the first Prime Minister of India?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Diwali</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Raksha Bandhan</t>
+          <t>Sardar Patel</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Holi</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Janmashtami</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Raksha Bandhan</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which state is known as the Spice Garden of India?</t>
+          <t>Which Indian state is the largest producer of spices?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Assam</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Meghalaya</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2920,252 +2920,252 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What is India's global rank in military strength (2024)?</t>
+          <t>Which Indian state has the longest coastline?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Indian city has Asia’s largest wholesale spice market?</t>
+          <t>What is the name of the Indian Parliament building?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Rashtrapati Bhavan</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Vidhan Sabha</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Sansad Bhavan</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which state has two capitals (summer and winter)?</t>
+          <t>Where is the headquarters of the Reserve Bank of India?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Indian state has its own constitution?</t>
+          <t>Which city is called the Yoga Capital of the World?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Haridwar</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir</t>
+          <t>Rishikesh</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Indian city is called the Pink City?</t>
+          <t>Which sector contributes the most to India's GDP?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Agra</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What is the capital of India?</t>
+          <t>What is India’s GDP rank globally in 2024?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Indian state has the largest area?</t>
+          <t>India shares its border with how many countries?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
